--- a/سجل_توثيق_مناقشات_التخرج_نادي_الجسور_2026.xlsx
+++ b/سجل_توثيق_مناقشات_التخرج_نادي_الجسور_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="سجل المناقشات المقبولة" sheetId="1" r:id="rId1"/>
+    <sheet name="سجل المناقشات" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,169 +397,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:I3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="28.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>رمز الطلب</v>
+        <v>عنوان المناقشة</v>
       </c>
       <c r="B1" t="str">
-        <v>تاريخ القبول / التسجيل</v>
+        <v>اسم الطالب</v>
       </c>
       <c r="C1" t="str">
-        <v>الاسم واللقب</v>
+        <v>اللجنة</v>
       </c>
       <c r="D1" t="str">
-        <v>التخصص</v>
+        <v>التاريخ</v>
       </c>
       <c r="E1" t="str">
-        <v>عنوان المذكرة</v>
+        <v>القاعة</v>
       </c>
       <c r="F1" t="str">
-        <v>رئيس اللجنة</v>
+        <v>الساعة</v>
       </c>
       <c r="G1" t="str">
-        <v>الأستاذ المشرف</v>
+        <v>المصور المتكفل بالتصوير</v>
       </c>
       <c r="H1" t="str">
-        <v>الأستاذ المناقش</v>
+        <v>رقم الهاتف</v>
       </c>
       <c r="I1" t="str">
-        <v>القاعة</v>
-      </c>
-      <c r="J1" t="str">
-        <v>يوم المناقشة</v>
-      </c>
-      <c r="K1" t="str">
-        <v>التوقيت</v>
-      </c>
-      <c r="L1" t="str">
-        <v>رقم الهاتف</v>
-      </c>
-      <c r="M1" t="str">
-        <v>معرف التيليجرام</v>
-      </c>
-      <c r="N1" t="str">
-        <v>اسم المصور المتكفل بالتصوير</v>
-      </c>
-      <c r="O1" t="str">
         <v>الحالة</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>JSR-101001</v>
+        <v>أحكام المعاملات المالية المعاصرة في الفقه الإسلامي</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-17 10:00:00</v>
+        <v>أيوب منصوري</v>
       </c>
       <c r="C2" t="str">
-        <v>أيوب منصوري</v>
+        <v>رئيس اللجنة: د. لخضر | المشرف: أ.د حميدي | المناقش: د. عمار</v>
       </c>
       <c r="D2" t="str">
-        <v>ماستر شريعة وقانون</v>
+        <v>2026-09-19</v>
       </c>
       <c r="E2" t="str">
-        <v>أحكام المعاملات المالية المعاصرة في الفقه الإسلامي</v>
+        <v>قاعة 04</v>
       </c>
       <c r="F2" t="str">
-        <v>د. لخضر حميدي</v>
+        <v>09:00</v>
       </c>
       <c r="G2" t="str">
-        <v>أ.د بلقاسم زروقي</v>
+        <v>عبد الرحيم</v>
       </c>
       <c r="H2" t="str">
-        <v>د. عمار بن صالح</v>
+        <v>0555123456</v>
       </c>
       <c r="I2" t="str">
-        <v>قاعة 04</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2026-09-19</v>
-      </c>
-      <c r="K2" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="L2" t="str">
-        <v>0555123456</v>
-      </c>
-      <c r="M2" t="str">
-        <v>@Ayoub_Mansouri</v>
-      </c>
-      <c r="N2" t="str">
-        <v>عبد الرحيم</v>
-      </c>
-      <c r="O2" t="str">
         <v>مؤكد</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>JSR-101002</v>
+        <v>منهج الاستدلال العقدي عند أئمة المغرب الإسلامي</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-17 11:30:00</v>
+        <v>سارة بوجمعة</v>
       </c>
       <c r="C3" t="str">
-        <v>سارة بوجمعة</v>
+        <v>رئيس اللجنة: د. بلقاسم | المشرف: د. زروقي | المناقش: د. قادري</v>
       </c>
       <c r="D3" t="str">
-        <v>ماستر أصول الدين</v>
+        <v>2026-09-20</v>
       </c>
       <c r="E3" t="str">
-        <v>منهج الاستدلال العقدي عند أئمة المغرب الإسلامي</v>
+        <v>مدرج ج</v>
       </c>
       <c r="F3" t="str">
-        <v>د. بلقاسم</v>
+        <v>10:30</v>
       </c>
       <c r="G3" t="str">
-        <v>د. زروقي</v>
+        <v>لم يُعيّن بعد</v>
       </c>
       <c r="H3" t="str">
-        <v>د. قادري</v>
+        <v>0666987654</v>
       </c>
       <c r="I3" t="str">
-        <v>مدرج ج</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2026-09-20</v>
-      </c>
-      <c r="K3" t="str">
-        <v>10:30</v>
-      </c>
-      <c r="L3" t="str">
-        <v>0666987654</v>
-      </c>
-      <c r="M3" t="str">
-        <v>@Sarah_B</v>
-      </c>
-      <c r="N3" t="str">
-        <v>لم يُعيّن بعد (يكتب يدوياً هنا)</v>
-      </c>
-      <c r="O3" t="str">
         <v>جديد</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/سجل_توثيق_مناقشات_التخرج_نادي_الجسور_2026.xlsx
+++ b/سجل_توثيق_مناقشات_التخرج_نادي_الجسور_2026.xlsx
@@ -397,109 +397,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:F4"/>
   <cols>
-    <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>عنوان المناقشة</v>
+        <v>اسم الطالب المناقش</v>
       </c>
       <c r="B1" t="str">
-        <v>اسم الطالب</v>
+        <v>القاعة</v>
       </c>
       <c r="C1" t="str">
-        <v>اللجنة</v>
+        <v>التاريخ</v>
       </c>
       <c r="D1" t="str">
-        <v>التاريخ</v>
+        <v>الساعة</v>
       </c>
       <c r="E1" t="str">
-        <v>القاعة</v>
+        <v>أسماء اللجنة</v>
       </c>
       <c r="F1" t="str">
-        <v>الساعة</v>
-      </c>
-      <c r="G1" t="str">
-        <v>المصور المتكفل بالتصوير</v>
-      </c>
-      <c r="H1" t="str">
-        <v>رقم الهاتف</v>
-      </c>
-      <c r="I1" t="str">
-        <v>الحالة</v>
+        <v>اسم الذي سيصور</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>أحكام المعاملات المالية المعاصرة في الفقه الإسلامي</v>
+        <v>محمد أمين بلقاسم</v>
       </c>
       <c r="B2" t="str">
-        <v>أيوب منصوري</v>
+        <v>قاعة المناقشات 01</v>
       </c>
       <c r="C2" t="str">
-        <v>رئيس اللجنة: د. لخضر | المشرف: أ.د حميدي | المناقش: د. عمار</v>
+        <v>2026-09-19</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-09-19</v>
+        <v>09:00</v>
       </c>
       <c r="E2" t="str">
-        <v>قاعة 04</v>
+        <v>الرئيس: أ.د. عبد الله مزيان | المشرف: د. بلقاسم بوداود | المناقش: د. عمر عثماني</v>
       </c>
       <c r="F2" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="G2" t="str">
-        <v>عبد الرحيم</v>
-      </c>
-      <c r="H2" t="str">
-        <v>0555123456</v>
-      </c>
-      <c r="I2" t="str">
-        <v>مؤكد</v>
+        <v>أحمد خليل (عضو نادي الجسور)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>منهج الاستدلال العقدي عند أئمة المغرب الإسلامي</v>
+        <v>سارة بن عيسى</v>
       </c>
       <c r="B3" t="str">
-        <v>سارة بوجمعة</v>
+        <v>المدرج ج (Amphi C)</v>
       </c>
       <c r="C3" t="str">
-        <v>رئيس اللجنة: د. بلقاسم | المشرف: د. زروقي | المناقش: د. قادري</v>
+        <v>2026-09-19</v>
       </c>
       <c r="D3" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="E3" t="str">
+        <v>الرئيس: د. فاطمة الزهراء بن حمزة | المشرف: أ.د. حكيم دراجي | المناقش: د. كمال لعريبي</v>
+      </c>
+      <c r="F3" t="str">
+        <v>ياسين قرشي (نادي الجسور)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>عبد النور رحماني</v>
+      </c>
+      <c r="B4" t="str">
+        <v>مخبر أبحاث الذكاء الاصطناعي</v>
+      </c>
+      <c r="C4" t="str">
         <v>2026-09-20</v>
       </c>
-      <c r="E3" t="str">
-        <v>مدرج ج</v>
-      </c>
-      <c r="F3" t="str">
-        <v>10:30</v>
-      </c>
-      <c r="G3" t="str">
-        <v>لم يُعيّن بعد</v>
-      </c>
-      <c r="H3" t="str">
-        <v>0666987654</v>
-      </c>
-      <c r="I3" t="str">
-        <v>جديد</v>
+      <c r="D4" t="str">
+        <v>14:00</v>
+      </c>
+      <c r="E4" t="str">
+        <v>الرئيس: د. سمير بن علي | المشرف: أ.د. مراد بن يحيى | المناقش: د. عمار شريفي</v>
+      </c>
+      <c r="F4" t="str">
+        <v>أسامة حداد (نادي الجسور)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>